--- a/uploads/data_entry.xlsx
+++ b/uploads/data_entry.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neerd\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F80A94-74DE-40C3-984A-63333118E46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C873502-0062-40DB-810D-3C87116F3A6E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,83 +19,169 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="17">
-  <si>
-    <t>Nomor_Entry</t>
-  </si>
-  <si>
-    <t>Kecamatan</t>
-  </si>
-  <si>
-    <t>Desa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+  <si>
+    <t>MOJOWARNO</t>
+  </si>
+  <si>
+    <t>bachtiar</t>
+  </si>
+  <si>
+    <t>199805292025041008</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NO ENTRI</t>
+  </si>
+  <si>
+    <t>NOPOL</t>
+  </si>
+  <si>
+    <t>NAMA / ALAMAT</t>
+  </si>
+  <si>
+    <t>DESA</t>
+  </si>
+  <si>
+    <t>KECAMATAN</t>
+  </si>
+  <si>
+    <t>POTENSI</t>
+  </si>
+  <si>
+    <t>TGCETAK</t>
+  </si>
+  <si>
+    <t>S 2726 XG</t>
+  </si>
+  <si>
+    <t>MOHAMMAD UBAIDILLAH</t>
+  </si>
+  <si>
+    <t>DS KEDAWONG RW 02/03</t>
+  </si>
+  <si>
+    <t>DS KEDAWONG</t>
+  </si>
+  <si>
+    <t>DIWEK</t>
+  </si>
+  <si>
+    <t>S 4176 OCU</t>
+  </si>
+  <si>
+    <t>WARTINI</t>
+  </si>
+  <si>
+    <t>JL SUMBERBOTO NO 395</t>
+  </si>
+  <si>
+    <t>DS MOJODUWUR</t>
+  </si>
+  <si>
+    <t>S 2413 OAM</t>
+  </si>
+  <si>
+    <t>YUNI INDRAYANTI</t>
+  </si>
+  <si>
+    <t>WEDANI</t>
+  </si>
+  <si>
+    <t>DS BADANG</t>
+  </si>
+  <si>
+    <t>NGORO</t>
+  </si>
+  <si>
+    <t>S 5233 OCI</t>
+  </si>
+  <si>
+    <t>WIWIK HIDAYATI</t>
+  </si>
+  <si>
+    <t>DSN. GENUKWATU</t>
+  </si>
+  <si>
+    <t>DS GENUKWATU</t>
+  </si>
+  <si>
+    <t>S 5470 OBE</t>
+  </si>
+  <si>
+    <t>FANDI PRAWIRA KUSUMA</t>
+  </si>
+  <si>
+    <t>JL SUPRIYADI I/2</t>
+  </si>
+  <si>
+    <t>DS NGORO</t>
+  </si>
+  <si>
+    <t>S 5080 OBT</t>
+  </si>
+  <si>
+    <t>INDRA WATI</t>
+  </si>
+  <si>
+    <t>DSN MANCILAN</t>
+  </si>
+  <si>
+    <t>S 4150 OAK</t>
+  </si>
+  <si>
+    <t>SAMSUDIN</t>
+  </si>
+  <si>
+    <t>BAKALAN</t>
+  </si>
+  <si>
+    <t>DS PULOREJO</t>
+  </si>
+  <si>
+    <t>S 3781 OAK</t>
+  </si>
+  <si>
+    <t>ABD HAKIM</t>
+  </si>
+  <si>
+    <t>PAYAK SANTREN</t>
+  </si>
+  <si>
+    <t>DS REJOAGUNG</t>
+  </si>
+  <si>
+    <t>196904231998031004</t>
+  </si>
+  <si>
+    <t>seno</t>
+  </si>
+  <si>
+    <t>199909162025042006</t>
+  </si>
+  <si>
+    <t>hesti</t>
   </si>
   <si>
     <t>ID_Login</t>
   </si>
   <si>
     <t>Password</t>
-  </si>
-  <si>
-    <t>MOJOWARNO</t>
-  </si>
-  <si>
-    <t>GONDEK</t>
-  </si>
-  <si>
-    <t>bachtiar</t>
-  </si>
-  <si>
-    <t>PENGGARON</t>
-  </si>
-  <si>
-    <t>REJOSLAMET</t>
-  </si>
-  <si>
-    <t>SUKOMULYO</t>
-  </si>
-  <si>
-    <t>LATSARI</t>
-  </si>
-  <si>
-    <t>JAPANAN</t>
-  </si>
-  <si>
-    <t>GROBOGAN</t>
-  </si>
-  <si>
-    <t>yafet</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
-    <t>199805292025041008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,7 +192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -120,35 +200,42 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -210,7 +297,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -262,7 +349,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -456,177 +543,531 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070054E2-8F5B-4478-9730-6529533E558B}">
-  <dimension ref="A1:E9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="28" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="6"/>
+      <c r="J1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10">
+        <v>2603008725</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="11">
+        <v>153600</v>
+      </c>
+      <c r="H2" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10">
+        <v>2603885421</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G4" s="11">
+        <v>235800</v>
+      </c>
+      <c r="H4" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2603005947</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="11">
+        <v>168500</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>2603007008</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="11">
+        <v>234100</v>
+      </c>
+      <c r="H8" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10">
+        <v>2603003799</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="11">
+        <v>240700</v>
+      </c>
+      <c r="H10" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>6</v>
+      </c>
+      <c r="B12" s="10">
+        <v>2603009295</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="11">
+        <v>210900</v>
+      </c>
+      <c r="H12" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>7</v>
+      </c>
+      <c r="B14" s="10">
+        <v>2603001691</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="11">
+        <v>168500</v>
+      </c>
+      <c r="H14" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>2602075217</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2602084205</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="K14" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2602023458</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2602062712</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>2602085861</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>2602087144</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2602010333</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>15</v>
+      <c r="B16" s="10">
+        <v>2603002935</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="11">
+        <v>196800</v>
+      </c>
+      <c r="H16" s="8">
+        <v>46084</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J25" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="J2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/data_entry.xlsx
+++ b/uploads/data_entry.xlsx
@@ -222,10 +222,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -543,7 +543,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -622,14 +622,14 @@
       <c r="G2" s="11">
         <v>153600</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>46084</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -643,10 +643,10 @@
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="8"/>
+      <c r="H3" s="7"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
@@ -670,14 +670,14 @@
       <c r="G4" s="11">
         <v>235800</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>46084</v>
       </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -691,10 +691,10 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -718,14 +718,14 @@
       <c r="G6" s="11">
         <v>168500</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>46084</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>47</v>
       </c>
     </row>
@@ -739,10 +739,10 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -766,14 +766,14 @@
       <c r="G8" s="11">
         <v>234100</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>46084</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -787,10 +787,10 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="8"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -814,14 +814,14 @@
       <c r="G10" s="11">
         <v>240700</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>46084</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -835,10 +835,10 @@
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="8"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -862,14 +862,14 @@
       <c r="G12" s="11">
         <v>210900</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>46084</v>
       </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>47</v>
       </c>
     </row>
@@ -883,10 +883,10 @@
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="7"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -910,14 +910,14 @@
       <c r="G14" s="11">
         <v>168500</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>46084</v>
       </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -931,10 +931,10 @@
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="11"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -958,14 +958,14 @@
       <c r="G16" s="11">
         <v>196800</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>46084</v>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -979,10 +979,10 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="8"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J25" s="4" t="s">
@@ -991,6 +991,62 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A4:A5"/>
@@ -1007,62 +1063,6 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
